--- a/projetos/gestao-ia-planilhas/produto/kit-advogados/07-proposta-de-honorarios.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-advogados/07-proposta-de-honorarios.xlsx
@@ -244,7 +244,9 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -955,7 +957,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="28" customHeight="1">
       <c r="A1" s="5">
         <f>Config!$B$4&amp;" · Proposta de honorários · "&amp;TEXT(DAY($E$4),"00")&amp;"/"&amp;TEXT(MONTH($E$4),"00")&amp;"/"&amp;YEAR($E$4)</f>
         <v/>
@@ -1653,13 +1655,14 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="A50:E50"/>
     <mergeCell ref="B8:E8"/>
     <mergeCell ref="A48:E48"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A49:E49"/>
     <mergeCell ref="A47:E47"/>
+    <mergeCell ref="A1:E1"/>
     <mergeCell ref="B21:D21"/>
     <mergeCell ref="A3:E3"/>
   </mergeCells>
@@ -1705,7 +1708,7 @@
     <col width="14" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="28" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Configurações</t>
@@ -2017,7 +2020,8 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
-  <mergeCells count="1">
+  <mergeCells count="2">
+    <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2048,7 +2052,7 @@
     <col width="34" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="28" customHeight="1">
       <c r="A1" s="5">
         <f>Config!$B$4&amp;" · Registro de propostas · "&amp;Config!$B$5</f>
         <v/>
@@ -4650,11 +4654,12 @@
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <autoFilter ref="A8:M108"/>
-  <mergeCells count="13">
+  <mergeCells count="14">
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="I4:J4"/>
+    <mergeCell ref="A1:M1"/>
     <mergeCell ref="C5:D5"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="G5:H5"/>

--- a/projetos/gestao-ia-planilhas/produto/kit-advogados/07-proposta-de-honorarios.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-advogados/07-proposta-de-honorarios.xlsx
@@ -835,7 +835,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Em Registro, atualize a situação quando o cliente responder. O topo mostra quantas estão aguardando, fechadas, perdidas e a taxa de fechamento.</t>
+          <t>Em Registro, atualize a situação quando o cliente responder. O topo mostra quantas estão aguardando, fechadas, perdidas e a taxa de fechamento. No exemplo, o Registro traz as 10 propostas mais recentes do funil da planilha 15 (as mesmas, com os mesmos valores); a 15 guarda o funil completo com etapas, origem e motivo de perda.</t>
         </is>
       </c>
     </row>
@@ -859,7 +859,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Copie a proposta e peça à IA para revisar clareza e tom antes de enviar, ou para escrever a mensagem de acompanhamento de uma proposta sem resposta. Os valores vêm do Simulador (planilha 06).</t>
+          <t>Copie a proposta e use o prompt "Honorários 04 · Texto de apresentação da proposta" da biblioteca do kit antes de enviar, ou "Honorários 02 · Revisar a proposta pela margem" para conferir o valor. Os valores vêm do Simulador (planilha 06).</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Excel 2019 ou mais novo, Microsoft 365 ou Google Sheets. No celular abre nos aplicativos; para preencher, use o computador.</t>
+          <t>Excel 2016 ou mais novo, Microsoft 365 ou Google Sheets (só funções do Excel 2007+; nada de MÍNIMOSES, MÁXIMOSES ou UNIRTEXTO). No celular abre nos aplicativos; para preencher, use o computador.</t>
         </is>
       </c>
     </row>
@@ -958,9 +958,9 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="5">
+      <c r="A1" s="5" t="str">
         <f>Config!$B$4&amp;" · Proposta de honorários · "&amp;TEXT(DAY($E$4),"00")&amp;"/"&amp;TEXT(MONTH($E$4),"00")&amp;"/"&amp;YEAR($E$4)</f>
-        <v/>
+        <v>Ferraz &amp; Lima Advocacia (exemplo fictício) · Proposta de honorários · 14/09/2026</v>
       </c>
     </row>
     <row r="2">
@@ -971,9 +971,9 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7">
+      <c r="A3" s="7" t="str">
         <f>Config!$B$7&amp;" · "&amp;Config!$B$8&amp;" · "&amp;Config!$B$9</f>
-        <v/>
+        <v>(11) 0000-0000 · contato@exemplo.com.br · Rua Exemplo, 100 · São Paulo · SP</v>
       </c>
     </row>
     <row r="4">
@@ -984,7 +984,7 @@
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>2026-014</t>
+          <t>2026-023</t>
         </is>
       </c>
       <c r="D4" s="8" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="E4" s="10">
         <f>TODAY()</f>
-        <v/>
+        <v>46279.0</v>
       </c>
     </row>
     <row r="5">
@@ -1035,7 +1035,7 @@
       </c>
       <c r="E6" s="12">
         <f>E4+E5</f>
-        <v/>
+        <v>46294.0</v>
       </c>
     </row>
     <row r="7">
@@ -1237,11 +1237,11 @@
       </c>
       <c r="D20" s="21">
         <f>SUM(D12:D19)</f>
-        <v/>
+        <v>53</v>
       </c>
       <c r="E20" s="22">
         <f>SUM(E12:E19)</f>
-        <v/>
+        <v>4500</v>
       </c>
     </row>
     <row r="21">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="E24" s="24">
         <f>$E$20*B24</f>
-        <v/>
+        <v>1800</v>
       </c>
     </row>
     <row r="25">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="E25" s="24">
         <f>$E$20-E24</f>
-        <v/>
+        <v>2700</v>
       </c>
     </row>
     <row r="26">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="E26" s="24">
         <f>IF(B25=0,0,E25/B25)</f>
-        <v/>
+        <v>900</v>
       </c>
     </row>
     <row r="27">
@@ -1375,59 +1375,59 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="26">
+      <c r="A31" s="26" t="str">
         <f>IF($E$24=0,"","Entrada")</f>
-        <v/>
-      </c>
-      <c r="B31" s="27">
+        <v>Entrada</v>
+      </c>
+      <c r="B31" s="27" t="str">
         <f>IF($E$24=0,"","Na aceitação da proposta")</f>
-        <v/>
+        <v>Na aceitação da proposta</v>
       </c>
       <c r="C31" s="24">
         <f>IF($E$24=0,"",$E$24)</f>
-        <v/>
+        <v>1800</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="26">
+      <c r="A32" s="26" t="str">
         <f>IF(1&gt;$B$25,"","Parcela 1 de "&amp;$B$25)</f>
-        <v/>
+        <v>Parcela 1 de 3</v>
       </c>
       <c r="B32" s="12">
         <f>IF(1&gt;$B$25,"",$E$4+$B$26+(1-1)*$B$27)</f>
-        <v/>
+        <v>46309.0</v>
       </c>
       <c r="C32" s="24">
         <f>IF(1&gt;$B$25,"",$E$26)</f>
-        <v/>
+        <v>900</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="26">
+      <c r="A33" s="26" t="str">
         <f>IF(2&gt;$B$25,"","Parcela 2 de "&amp;$B$25)</f>
-        <v/>
+        <v>Parcela 2 de 3</v>
       </c>
       <c r="B33" s="12">
         <f>IF(2&gt;$B$25,"",$E$4+$B$26+(2-1)*$B$27)</f>
-        <v/>
+        <v>46339.0</v>
       </c>
       <c r="C33" s="24">
         <f>IF(2&gt;$B$25,"",$E$26)</f>
-        <v/>
+        <v>900</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="26">
+      <c r="A34" s="26" t="str">
         <f>IF(3&gt;$B$25,"","Parcela 3 de "&amp;$B$25)</f>
-        <v/>
+        <v>Parcela 3 de 3</v>
       </c>
       <c r="B34" s="12">
         <f>IF(3&gt;$B$25,"",$E$4+$B$26+(3-1)*$B$27)</f>
-        <v/>
+        <v>46369.0</v>
       </c>
       <c r="C34" s="24">
         <f>IF(3&gt;$B$25,"",$E$26)</f>
-        <v/>
+        <v>900</v>
       </c>
     </row>
     <row r="35">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="C44" s="22">
         <f>SUM(C31:C43)</f>
-        <v/>
+        <v>4500</v>
       </c>
     </row>
     <row r="46">
@@ -1608,9 +1608,9 @@
       <c r="E49" s="16" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="26">
+      <c r="A50" s="26" t="str">
         <f>"Forma de pagamento: "&amp;$E$27&amp;". Esta proposta é válida até "&amp;TEXT(DAY($E$6),"00")&amp;"/"&amp;TEXT(MONTH($E$6),"00")&amp;"/"&amp;YEAR($E$6)&amp;"."</f>
-        <v/>
+        <v>Forma de pagamento: Pix. Esta proposta é válida até 29/09/2026.</v>
       </c>
       <c r="B50" s="28" t="n"/>
       <c r="C50" s="28" t="n"/>
@@ -1637,13 +1637,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="30">
+      <c r="A56" s="30" t="str">
         <f>$B$5</f>
-        <v/>
-      </c>
-      <c r="D56" s="30">
+        <v>Roberto Almeida</v>
+      </c>
+      <c r="D56" s="30" t="str">
         <f>Config!$B$10&amp;" · "&amp;Config!$B$4</f>
-        <v/>
+        <v>Marina Ferraz · Ferraz &amp; Lima Advocacia (exemplo fictício)</v>
       </c>
     </row>
     <row r="58">
@@ -1718,7 +1718,7 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>Células amarelas: você preenche. Os dados do escritório aparecem no cabeçalho da proposta.</t>
+          <t>Células amarelas: você preenche. Os dados do escritório aparecem no cabeçalho da proposta: antes da primeira proposta real, troque o nome (tire o "(exemplo fictício)"), telefone, e-mail e endereço.</t>
         </is>
       </c>
     </row>
@@ -1754,7 +1754,7 @@
       </c>
       <c r="B6" s="12">
         <f>TODAY()</f>
-        <v/>
+        <v>46279.0</v>
       </c>
     </row>
     <row r="7">
@@ -1802,6 +1802,13 @@
       <c r="B10" s="9" t="inlineStr">
         <is>
           <t>Marina Ferraz</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>O nome acima sai impresso no cabeçalho e na assinatura da proposta. Apague o "(exemplo fictício)" antes de enviar a primeira proposta.</t>
         </is>
       </c>
     </row>
@@ -2053,9 +2060,9 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="5">
+      <c r="A1" s="5" t="str">
         <f>Config!$B$4&amp;" · Registro de propostas · "&amp;Config!$B$5</f>
-        <v/>
+        <v>Ferraz &amp; Lima Advocacia (exemplo fictício) · Registro de propostas · Setembro de 2026</v>
       </c>
     </row>
     <row r="2">
@@ -2106,32 +2113,32 @@
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="39">
         <f>COUNTIF($J$9:$J$108,"Enviada")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="B5" s="32" t="n"/>
       <c r="C5" s="40">
         <f>COUNTIF($J$9:$J$108,"Fechada")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="D5" s="34" t="n"/>
       <c r="E5" s="41">
         <f>COUNTIF($J$9:$J$108,"Perdida")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="F5" s="36" t="n"/>
       <c r="G5" s="42">
         <f>SUMIFS($G$9:$G$108,$J$9:$J$108,"Fechada")</f>
-        <v/>
+        <v>26100</v>
       </c>
       <c r="H5" s="38" t="n"/>
       <c r="I5" s="43">
         <f>IFERROR(C5/(C5+E5),0)</f>
-        <v/>
+        <v>0.6</v>
       </c>
       <c r="J5" s="32" t="n"/>
       <c r="K5" s="44">
         <f>SUMIFS($G$9:$G$108,$J$9:$J$108,"Enviada")</f>
-        <v/>
+        <v>40400</v>
       </c>
       <c r="L5" s="32" t="n"/>
     </row>
@@ -2205,244 +2212,237 @@
     <row r="9">
       <c r="A9" s="13" t="inlineStr">
         <is>
-          <t>2026-005</t>
-        </is>
-      </c>
-      <c r="B9" s="10" t="n">
-        <v>46183</v>
+          <t>2026-023</t>
+        </is>
+      </c>
+      <c r="B9" s="10">
+        <f>TODAY()</f>
+        <v>46279.0</v>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>Padaria do Sol Ltda</t>
+          <t>Roberto Almeida</t>
         </is>
       </c>
       <c r="D9" s="13" t="inlineStr">
         <is>
-          <t>Empresarial</t>
+          <t>Cível</t>
         </is>
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>Revisão dos contratos com fornecedores</t>
+          <t>Discussão de contrato de prestação de serviços</t>
         </is>
       </c>
       <c r="F9" s="13" t="inlineStr">
         <is>
-          <t>Fixo</t>
+          <t>Misto</t>
         </is>
       </c>
       <c r="G9" s="45" t="n">
-        <v>4800</v>
+        <v>4500</v>
       </c>
       <c r="H9" s="11" t="n">
         <v>15</v>
       </c>
       <c r="I9" s="12">
         <f>IF(OR(B9="",H9=""),"",B9+H9)</f>
-        <v/>
+        <v>46294.0</v>
       </c>
       <c r="J9" s="13" t="inlineStr">
         <is>
-          <t>Fechada</t>
-        </is>
-      </c>
-      <c r="K9" s="10" t="n">
-        <v>46191</v>
-      </c>
+          <t>Enviada</t>
+        </is>
+      </c>
+      <c r="K9" s="10" t="n"/>
       <c r="L9" s="26">
         <f>IF(A9="","",IF(J9&lt;&gt;"Enviada","",IF(I9="","",IF(I9&lt;TODAY(),"Validade vencida · retomar contato",IF(I9-TODAY()&lt;=3,"Vence em até 3 dias","")))))</f>
         <v/>
       </c>
-      <c r="M9" s="9" t="inlineStr"/>
+      <c r="M9" s="9" t="inlineStr">
+        <is>
+          <t>Mais 15% de êxito · é a proposta da aba Proposta da planilha 07</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="13" t="inlineStr">
         <is>
-          <t>2026-006</t>
+          <t>2026-019</t>
         </is>
       </c>
       <c r="B10" s="10" t="n">
-        <v>46195</v>
+        <v>46265</v>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>Ana Beatriz Moreira</t>
+          <t>José Antônio Ribeiro</t>
         </is>
       </c>
       <c r="D10" s="13" t="inlineStr">
         <is>
-          <t>Trabalhista</t>
+          <t>Previdenciário</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>Processo trabalhista · fase inicial</t>
+          <t>Revisão de benefício</t>
         </is>
       </c>
       <c r="F10" s="13" t="inlineStr">
         <is>
-          <t>Êxito</t>
+          <t>Fixo</t>
         </is>
       </c>
       <c r="G10" s="45" t="n">
-        <v>6000</v>
+        <v>4200</v>
       </c>
       <c r="H10" s="11" t="n">
         <v>15</v>
       </c>
       <c r="I10" s="12">
         <f>IF(OR(B10="",H10=""),"",B10+H10)</f>
-        <v/>
+        <v>46280.0</v>
       </c>
       <c r="J10" s="13" t="inlineStr">
         <is>
-          <t>Perdida</t>
-        </is>
-      </c>
-      <c r="K10" s="10" t="n">
-        <v>46208</v>
-      </c>
-      <c r="L10" s="26">
+          <t>Enviada</t>
+        </is>
+      </c>
+      <c r="K10" s="10" t="n"/>
+      <c r="L10" s="26" t="str">
         <f>IF(A10="","",IF(J10&lt;&gt;"Enviada","",IF(I10="","",IF(I10&lt;TODAY(),"Validade vencida · retomar contato",IF(I10-TODAY()&lt;=3,"Vence em até 3 dias","")))))</f>
-        <v/>
+        <v>Vence em até 3 dias</v>
       </c>
       <c r="M10" s="9" t="inlineStr">
         <is>
-          <t>Fechou com outro escritório</t>
+          <t>Sem retorno; ligar</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="13" t="inlineStr">
         <is>
-          <t>2026-007</t>
+          <t>2026-018</t>
         </is>
       </c>
       <c r="B11" s="10" t="n">
-        <v>46204</v>
+        <v>46263</v>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>Construtora Horizonte</t>
+          <t>Patrícia Gomes</t>
         </is>
       </c>
       <c r="D11" s="13" t="inlineStr">
         <is>
-          <t>Cível</t>
+          <t>Família</t>
         </is>
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>Disputa sobre contrato de obra</t>
+          <t>Inventário</t>
         </is>
       </c>
       <c r="F11" s="13" t="inlineStr">
         <is>
-          <t>Misto</t>
+          <t>Fixo</t>
         </is>
       </c>
       <c r="G11" s="45" t="n">
-        <v>12000</v>
+        <v>10500</v>
       </c>
       <c r="H11" s="11" t="n">
         <v>15</v>
       </c>
       <c r="I11" s="12">
         <f>IF(OR(B11="",H11=""),"",B11+H11)</f>
-        <v/>
+        <v>46278.0</v>
       </c>
       <c r="J11" s="13" t="inlineStr">
         <is>
-          <t>Fechada</t>
-        </is>
-      </c>
-      <c r="K11" s="10" t="n">
-        <v>46213</v>
-      </c>
-      <c r="L11" s="26">
+          <t>Enviada</t>
+        </is>
+      </c>
+      <c r="K11" s="10" t="n"/>
+      <c r="L11" s="26" t="str">
         <f>IF(A11="","",IF(J11&lt;&gt;"Enviada","",IF(I11="","",IF(I11&lt;TODAY(),"Validade vencida · retomar contato",IF(I11-TODAY()&lt;=3,"Vence em até 3 dias","")))))</f>
-        <v/>
-      </c>
-      <c r="M11" s="9" t="inlineStr">
-        <is>
-          <t>Entrada de 30%</t>
-        </is>
-      </c>
+        <v>Validade vencida · retomar contato</v>
+      </c>
+      <c r="M11" s="9" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="13" t="inlineStr">
         <is>
-          <t>2026-008</t>
+          <t>2026-017</t>
         </is>
       </c>
       <c r="B12" s="10" t="n">
-        <v>46211</v>
+        <v>46260</v>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>Carlos Eduardo Nunes</t>
+          <t>Clínica Bem-Estar</t>
         </is>
       </c>
       <c r="D12" s="13" t="inlineStr">
         <is>
-          <t>Previdenciário</t>
+          <t>Empresarial</t>
         </is>
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
-          <t>Pedido de benefício · acompanhamento</t>
+          <t>Contratos com convênios</t>
         </is>
       </c>
       <c r="F12" s="13" t="inlineStr">
         <is>
-          <t>Êxito</t>
+          <t>Fixo</t>
         </is>
       </c>
       <c r="G12" s="45" t="n">
-        <v>5000</v>
+        <v>6800</v>
       </c>
       <c r="H12" s="11" t="n">
         <v>15</v>
       </c>
       <c r="I12" s="12">
         <f>IF(OR(B12="",H12=""),"",B12+H12)</f>
-        <v/>
+        <v>46275.0</v>
       </c>
       <c r="J12" s="13" t="inlineStr">
         <is>
-          <t>Fechada</t>
-        </is>
-      </c>
-      <c r="K12" s="10" t="n">
-        <v>46218</v>
-      </c>
-      <c r="L12" s="26">
+          <t>Enviada</t>
+        </is>
+      </c>
+      <c r="K12" s="10" t="n"/>
+      <c r="L12" s="26" t="str">
         <f>IF(A12="","",IF(J12&lt;&gt;"Enviada","",IF(I12="","",IF(I12&lt;TODAY(),"Validade vencida · retomar contato",IF(I12-TODAY()&lt;=3,"Vence em até 3 dias","")))))</f>
-        <v/>
+        <v>Validade vencida · retomar contato</v>
       </c>
       <c r="M12" s="9" t="inlineStr">
         <is>
-          <t>Valor estimado; recebe no fim</t>
+          <t>Reunião de apresentação feita; sem retorno</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>2026-009</t>
+          <t>2026-016</t>
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>46223</v>
+        <v>46254</v>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>Loja Verde Comércio</t>
+          <t>Transportadora Rota Sul</t>
         </is>
       </c>
       <c r="D13" s="13" t="inlineStr">
         <is>
-          <t>Empresarial</t>
+          <t>Trabalhista</t>
         </is>
       </c>
       <c r="E13" s="9" t="inlineStr">
@@ -2459,52 +2459,50 @@
         <v>14400</v>
       </c>
       <c r="H13" s="11" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="I13" s="12">
         <f>IF(OR(B13="",H13=""),"",B13+H13)</f>
-        <v/>
+        <v>46269.0</v>
       </c>
       <c r="J13" s="13" t="inlineStr">
         <is>
-          <t>Perdida</t>
-        </is>
-      </c>
-      <c r="K13" s="10" t="n">
-        <v>46238</v>
-      </c>
-      <c r="L13" s="26">
+          <t>Enviada</t>
+        </is>
+      </c>
+      <c r="K13" s="10" t="n"/>
+      <c r="L13" s="26" t="str">
         <f>IF(A13="","",IF(J13&lt;&gt;"Enviada","",IF(I13="","",IF(I13&lt;TODAY(),"Validade vencida · retomar contato",IF(I13-TODAY()&lt;=3,"Vence em até 3 dias","")))))</f>
-        <v/>
+        <v>Validade vencida · retomar contato</v>
       </c>
       <c r="M13" s="9" t="inlineStr">
         <is>
-          <t>Achou caro; retomar em janeiro</t>
+          <t>Pediu parcela mensal menor</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="13" t="inlineStr">
         <is>
-          <t>2026-010</t>
+          <t>2026-015</t>
         </is>
       </c>
       <c r="B14" s="10" t="n">
-        <v>46237</v>
+        <v>46248</v>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>Fernanda Castro</t>
+          <t>Agência Prisma</t>
         </is>
       </c>
       <c r="D14" s="13" t="inlineStr">
         <is>
-          <t>Família</t>
+          <t>Empresarial</t>
         </is>
       </c>
       <c r="E14" s="9" t="inlineStr">
         <is>
-          <t>Acordo entre as partes</t>
+          <t>Contratos e consultoria</t>
         </is>
       </c>
       <c r="F14" s="13" t="inlineStr">
@@ -2513,41 +2511,45 @@
         </is>
       </c>
       <c r="G14" s="45" t="n">
-        <v>7000</v>
+        <v>11000</v>
       </c>
       <c r="H14" s="11" t="n">
         <v>15</v>
       </c>
       <c r="I14" s="12">
         <f>IF(OR(B14="",H14=""),"",B14+H14)</f>
-        <v/>
+        <v>46263.0</v>
       </c>
       <c r="J14" s="13" t="inlineStr">
         <is>
-          <t>Fechada</t>
+          <t>Perdida</t>
         </is>
       </c>
       <c r="K14" s="10" t="n">
-        <v>46244</v>
+        <v>46267</v>
       </c>
       <c r="L14" s="26">
         <f>IF(A14="","",IF(J14&lt;&gt;"Enviada","",IF(I14="","",IF(I14&lt;TODAY(),"Validade vencida · retomar contato",IF(I14-TODAY()&lt;=3,"Vence em até 3 dias","")))))</f>
         <v/>
       </c>
-      <c r="M14" s="9" t="inlineStr"/>
+      <c r="M14" s="9" t="inlineStr">
+        <is>
+          <t>Preço · Cliente questiona as horas do recurso em andamento</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="13" t="inlineStr">
         <is>
-          <t>2026-011</t>
+          <t>2026-014</t>
         </is>
       </c>
       <c r="B15" s="10" t="n">
-        <v>46246</v>
+        <v>46240</v>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>Bistrô 42</t>
+          <t>Oficina Mecânica Central</t>
         </is>
       </c>
       <c r="D15" s="13" t="inlineStr">
@@ -2557,23 +2559,23 @@
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>Processo trabalhista · defesa</t>
+          <t>Ação trabalhista</t>
         </is>
       </c>
       <c r="F15" s="13" t="inlineStr">
         <is>
-          <t>Hora</t>
+          <t>Êxito</t>
         </is>
       </c>
       <c r="G15" s="45" t="n">
-        <v>8500</v>
+        <v>4400</v>
       </c>
       <c r="H15" s="11" t="n">
         <v>15</v>
       </c>
       <c r="I15" s="12">
         <f>IF(OR(B15="",H15=""),"",B15+H15)</f>
-        <v/>
+        <v>46255.0</v>
       </c>
       <c r="J15" s="13" t="inlineStr">
         <is>
@@ -2581,7 +2583,7 @@
         </is>
       </c>
       <c r="K15" s="10" t="n">
-        <v>46262</v>
+        <v>46259</v>
       </c>
       <c r="L15" s="26">
         <f>IF(A15="","",IF(J15&lt;&gt;"Enviada","",IF(I15="","",IF(I15&lt;TODAY(),"Validade vencida · retomar contato",IF(I15-TODAY()&lt;=3,"Vence em até 3 dias","")))))</f>
@@ -2589,33 +2591,32 @@
       </c>
       <c r="M15" s="9" t="inlineStr">
         <is>
-          <t>Estimativa de 65 horas; preferiu valor fixo</t>
+          <t>Sem resposta</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="13" t="inlineStr">
         <is>
-          <t>2026-012</t>
-        </is>
-      </c>
-      <c r="B16" s="10">
-        <f>TODAY()-12</f>
-        <v/>
+          <t>2026-013</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="n">
+        <v>46240</v>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>Clínica Bem-Estar</t>
+          <t>Marcos Vinícius Teles</t>
         </is>
       </c>
       <c r="D16" s="13" t="inlineStr">
         <is>
-          <t>Empresarial</t>
+          <t>Previdenciário</t>
         </is>
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
-          <t>Contratos com convênios</t>
+          <t>Planejamento previdenciário</t>
         </is>
       </c>
       <c r="F16" s="13" t="inlineStr">
@@ -2624,100 +2625,98 @@
         </is>
       </c>
       <c r="G16" s="45" t="n">
-        <v>9600</v>
+        <v>4500</v>
       </c>
       <c r="H16" s="11" t="n">
         <v>15</v>
       </c>
       <c r="I16" s="12">
         <f>IF(OR(B16="",H16=""),"",B16+H16)</f>
-        <v/>
+        <v>46255.0</v>
       </c>
       <c r="J16" s="13" t="inlineStr">
         <is>
-          <t>Enviada</t>
-        </is>
-      </c>
-      <c r="K16" s="10" t="n"/>
+          <t>Fechada</t>
+        </is>
+      </c>
+      <c r="K16" s="10" t="n">
+        <v>46253</v>
+      </c>
       <c r="L16" s="26">
         <f>IF(A16="","",IF(J16&lt;&gt;"Enviada","",IF(I16="","",IF(I16&lt;TODAY(),"Validade vencida · retomar contato",IF(I16-TODAY()&lt;=3,"Vence em até 3 dias","")))))</f>
         <v/>
       </c>
-      <c r="M16" s="9" t="inlineStr">
-        <is>
-          <t>Reunião de apresentação feita</t>
-        </is>
-      </c>
+      <c r="M16" s="9" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="13" t="inlineStr">
         <is>
-          <t>2026-013</t>
-        </is>
-      </c>
-      <c r="B17" s="10">
-        <f>TODAY()-20</f>
-        <v/>
+          <t>2026-012</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="n">
+        <v>46226</v>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>Escola Aurora</t>
+          <t>Loja Verde Comércio</t>
         </is>
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>Cível</t>
+          <t>Empresarial</t>
         </is>
       </c>
       <c r="E17" s="9" t="inlineStr">
         <is>
-          <t>Cobrança de mensalidades em atraso</t>
+          <t>Contratos e consultoria</t>
         </is>
       </c>
       <c r="F17" s="13" t="inlineStr">
         <is>
-          <t>Misto</t>
+          <t>Fixo</t>
         </is>
       </c>
       <c r="G17" s="45" t="n">
-        <v>6500</v>
+        <v>8400</v>
       </c>
       <c r="H17" s="11" t="n">
         <v>15</v>
       </c>
       <c r="I17" s="12">
         <f>IF(OR(B17="",H17=""),"",B17+H17)</f>
-        <v/>
+        <v>46241.0</v>
       </c>
       <c r="J17" s="13" t="inlineStr">
         <is>
-          <t>Enviada</t>
-        </is>
-      </c>
-      <c r="K17" s="10" t="n"/>
+          <t>Fechada</t>
+        </is>
+      </c>
+      <c r="K17" s="10" t="n">
+        <v>46245</v>
+      </c>
       <c r="L17" s="26">
         <f>IF(A17="","",IF(J17&lt;&gt;"Enviada","",IF(I17="","",IF(I17&lt;TODAY(),"Validade vencida · retomar contato",IF(I17-TODAY()&lt;=3,"Vence em até 3 dias","")))))</f>
         <v/>
       </c>
       <c r="M17" s="9" t="inlineStr">
         <is>
-          <t>Sem retorno; ligar</t>
+          <t>Três pareceres e revisão dos contratos com fornecedores</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
         <is>
-          <t>2026-014</t>
-        </is>
-      </c>
-      <c r="B18" s="10">
-        <f>TODAY()</f>
-        <v/>
+          <t>2026-009</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="n">
+        <v>46224</v>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>Roberto Almeida</t>
+          <t>Escola Aurora</t>
         </is>
       </c>
       <c r="D18" s="13" t="inlineStr">
@@ -2727,37 +2726,39 @@
       </c>
       <c r="E18" s="9" t="inlineStr">
         <is>
-          <t>Discussão de contrato de prestação de serviços</t>
+          <t>Assessoria mensal (12 meses)</t>
         </is>
       </c>
       <c r="F18" s="13" t="inlineStr">
         <is>
-          <t>Misto</t>
+          <t>Fixo</t>
         </is>
       </c>
       <c r="G18" s="45" t="n">
-        <v>4500</v>
+        <v>13200</v>
       </c>
       <c r="H18" s="11" t="n">
         <v>15</v>
       </c>
       <c r="I18" s="12">
         <f>IF(OR(B18="",H18=""),"",B18+H18)</f>
-        <v/>
+        <v>46239.0</v>
       </c>
       <c r="J18" s="13" t="inlineStr">
         <is>
-          <t>Enviada</t>
-        </is>
-      </c>
-      <c r="K18" s="10" t="n"/>
+          <t>Fechada</t>
+        </is>
+      </c>
+      <c r="K18" s="10" t="n">
+        <v>46237</v>
+      </c>
       <c r="L18" s="26">
         <f>IF(A18="","",IF(J18&lt;&gt;"Enviada","",IF(I18="","",IF(I18&lt;TODAY(),"Validade vencida · retomar contato",IF(I18-TODAY()&lt;=3,"Vence em até 3 dias","")))))</f>
         <v/>
       </c>
       <c r="M18" s="9" t="inlineStr">
         <is>
-          <t>Mais 15% de êxito · é a proposta da aba Proposta</t>
+          <t>R$ 1.100 por mês</t>
         </is>
       </c>
     </row>

--- a/projetos/gestao-ia-planilhas/produto/kit-advogados/07-proposta-de-honorarios.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-advogados/07-proposta-de-honorarios.xlsx
@@ -22,10 +22,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
-    <numFmt numFmtId="165" formatCode="&quot;R$&quot; #,##0.00;[Red]-&quot;R$&quot; #,##0.00"/>
-    <numFmt numFmtId="166" formatCode="&quot;R$&quot; #,##0;[Red]-&quot;R$&quot; #,##0"/>
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="166" formatCode="&quot;R$&quot; #,##0.00;[Red]-&quot;R$&quot; #,##0.00"/>
+    <numFmt numFmtId="167" formatCode="&quot;R$&quot; #,##0;[Red]-&quot;R$&quot; #,##0"/>
   </numFmts>
   <fonts count="17">
     <font>
@@ -253,7 +254,7 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -261,7 +262,7 @@
       <alignment horizontal="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -282,7 +283,7 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -290,14 +291,14 @@
     <xf numFmtId="1" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -335,16 +336,16 @@
     <xf numFmtId="3" fontId="12" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="1" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="4" fillId="2" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
   </cellXfs>
@@ -758,7 +759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -919,17 +920,29 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Ferraz &amp; Lima Advocacia é um escritório fictício. Clientes, processos, nomes e valores são inventados. Apague-os antes de começar. Datas de prazo do exemplo são relativas a hoje.</t>
+          <t>Ferraz &amp; Lima Advocacia é um escritório fictício. Clientes, processos, nomes e valores são inventados. Apague-os antes de começar.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="46" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
+          <t>Data de referência</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os seus dados, troque a data de referência em Config por =HOJE(): daí em diante ela acompanha o dia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="46" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
           <t>Suporte</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>suporte@seusociogestor.com.br · resposta em até 5 dias úteis · reembolso em até 7 dias pelo mesmo canal.</t>
         </is>
@@ -960,7 +973,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="5" t="str">
         <f>Config!$B$4&amp;" · Proposta de honorários · "&amp;TEXT(DAY($E$4),"00")&amp;"/"&amp;TEXT(MONTH($E$4),"00")&amp;"/"&amp;YEAR($E$4)</f>
-        <v>Ferraz &amp; Lima Advocacia (exemplo fictício) · Proposta de honorários · 14/09/2026</v>
+        <v>Ferraz &amp; Lima Advocacia (exemplo fictício) · Proposta de honorários · 17/09/2026</v>
       </c>
     </row>
     <row r="2">
@@ -994,7 +1007,7 @@
       </c>
       <c r="E4" s="10">
         <f>TODAY()</f>
-        <v>46279.0</v>
+        <v>46282.0</v>
       </c>
     </row>
     <row r="5">
@@ -1035,7 +1048,7 @@
       </c>
       <c r="E6" s="12">
         <f>E4+E5</f>
-        <v>46294.0</v>
+        <v>46297.0</v>
       </c>
     </row>
     <row r="7">
@@ -1302,7 +1315,7 @@
         </is>
       </c>
       <c r="E25" s="24">
-        <f>$E$20-E24</f>
+        <f>IF(AND(B25=0,$E$20-E24&gt;0),"ATENÇÃO: "&amp;FIXED($E$20-E24,2)&amp;" sem parcelas",$E$20-E24)</f>
         <v>2700</v>
       </c>
     </row>
@@ -1395,7 +1408,7 @@
       </c>
       <c r="B32" s="12">
         <f>IF(1&gt;$B$25,"",$E$4+$B$26+(1-1)*$B$27)</f>
-        <v>46309.0</v>
+        <v>46312.0</v>
       </c>
       <c r="C32" s="24">
         <f>IF(1&gt;$B$25,"",$E$26)</f>
@@ -1409,7 +1422,7 @@
       </c>
       <c r="B33" s="12">
         <f>IF(2&gt;$B$25,"",$E$4+$B$26+(2-1)*$B$27)</f>
-        <v>46339.0</v>
+        <v>46342.0</v>
       </c>
       <c r="C33" s="24">
         <f>IF(2&gt;$B$25,"",$E$26)</f>
@@ -1423,7 +1436,7 @@
       </c>
       <c r="B34" s="12">
         <f>IF(3&gt;$B$25,"",$E$4+$B$26+(3-1)*$B$27)</f>
-        <v>46369.0</v>
+        <v>46372.0</v>
       </c>
       <c r="C34" s="24">
         <f>IF(3&gt;$B$25,"",$E$26)</f>
@@ -1610,7 +1623,7 @@
     <row r="50">
       <c r="A50" s="26" t="str">
         <f>"Forma de pagamento: "&amp;$E$27&amp;". Esta proposta é válida até "&amp;TEXT(DAY($E$6),"00")&amp;"/"&amp;TEXT(MONTH($E$6),"00")&amp;"/"&amp;YEAR($E$6)&amp;"."</f>
-        <v>Forma de pagamento: Pix. Esta proposta é válida até 29/09/2026.</v>
+        <v>Forma de pagamento: Pix. Esta proposta é válida até 02/10/2026.</v>
       </c>
       <c r="B50" s="28" t="n"/>
       <c r="C50" s="28" t="n"/>
@@ -1673,7 +1686,7 @@
     <dataValidation sqref="E7" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=OFFSET(Config!$F$14,0,0,MAX(1,COUNTA(Config!$F$14:$F$33)),1)</formula1>
     </dataValidation>
-    <dataValidation sqref="B25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="whole" operator="between">
+    <dataValidation sqref="B25" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Parcelas do restante" error="Digite um número inteiro de 1 a 12. Use 0 apenas se a entrada quitar o valor todo." type="whole" operator="between">
       <formula1>0</formula1>
       <formula2>12</formula2>
     </dataValidation>
@@ -1752,9 +1765,8 @@
           <t>Data de referência</t>
         </is>
       </c>
-      <c r="B6" s="12">
-        <f>TODAY()</f>
-        <v>46279.0</v>
+      <c r="B6" s="12" t="n">
+        <v>46279</v>
       </c>
     </row>
     <row r="7">
@@ -2215,9 +2227,8 @@
           <t>2026-023</t>
         </is>
       </c>
-      <c r="B9" s="10">
-        <f>TODAY()</f>
-        <v>46279.0</v>
+      <c r="B9" s="10" t="n">
+        <v>46279</v>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
@@ -2312,7 +2323,7 @@
       <c r="K10" s="10" t="n"/>
       <c r="L10" s="26" t="str">
         <f>IF(A10="","",IF(J10&lt;&gt;"Enviada","",IF(I10="","",IF(I10&lt;TODAY(),"Validade vencida · retomar contato",IF(I10-TODAY()&lt;=3,"Vence em até 3 dias","")))))</f>
-        <v>Vence em até 3 dias</v>
+        <v>Validade vencida · retomar contato</v>
       </c>
       <c r="M10" s="9" t="inlineStr">
         <is>
@@ -4688,7 +4699,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation sqref="D9:D108" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D9:D108" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=OFFSET(Config!$D$14,0,0,MAX(1,COUNTA(Config!$D$14:$D$33)),1)</formula1>
     </dataValidation>
     <dataValidation sqref="F9:F108" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
@@ -4697,7 +4708,7 @@
     <dataValidation sqref="J9:J108" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=OFFSET(Config!$J$14,0,0,MAX(1,COUNTA(Config!$J$14:$J$33)),1)</formula1>
     </dataValidation>
-    <dataValidation sqref="B9:B108" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="date" operator="greaterThan">
+    <dataValidation sqref="B9:B108" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="date" operator="greaterThan">
       <formula1>1</formula1>
     </dataValidation>
   </dataValidations>

--- a/projetos/gestao-ia-planilhas/produto/kit-advogados/07-proposta-de-honorarios.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-advogados/07-proposta-de-honorarios.xlsx
@@ -973,7 +973,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="5" t="str">
         <f>Config!$B$4&amp;" · Proposta de honorários · "&amp;TEXT(DAY($E$4),"00")&amp;"/"&amp;TEXT(MONTH($E$4),"00")&amp;"/"&amp;YEAR($E$4)</f>
-        <v>Ferraz &amp; Lima Advocacia (exemplo fictício) · Proposta de honorários · 17/09/2026</v>
+        <v>Ferraz &amp; Lima Advocacia (exemplo fictício) · Proposta de honorários · 18/09/2026</v>
       </c>
     </row>
     <row r="2">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="E4" s="10">
         <f>TODAY()</f>
-        <v>46282.0</v>
+        <v>46283.0</v>
       </c>
     </row>
     <row r="5">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="E6" s="12">
         <f>E4+E5</f>
-        <v>46297.0</v>
+        <v>46298.0</v>
       </c>
     </row>
     <row r="7">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B32" s="12">
         <f>IF(1&gt;$B$25,"",$E$4+$B$26+(1-1)*$B$27)</f>
-        <v>46312.0</v>
+        <v>46313.0</v>
       </c>
       <c r="C32" s="24">
         <f>IF(1&gt;$B$25,"",$E$26)</f>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="B33" s="12">
         <f>IF(2&gt;$B$25,"",$E$4+$B$26+(2-1)*$B$27)</f>
-        <v>46342.0</v>
+        <v>46343.0</v>
       </c>
       <c r="C33" s="24">
         <f>IF(2&gt;$B$25,"",$E$26)</f>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="B34" s="12">
         <f>IF(3&gt;$B$25,"",$E$4+$B$26+(3-1)*$B$27)</f>
-        <v>46372.0</v>
+        <v>46373.0</v>
       </c>
       <c r="C34" s="24">
         <f>IF(3&gt;$B$25,"",$E$26)</f>
@@ -1623,7 +1623,7 @@
     <row r="50">
       <c r="A50" s="26" t="str">
         <f>"Forma de pagamento: "&amp;$E$27&amp;". Esta proposta é válida até "&amp;TEXT(DAY($E$6),"00")&amp;"/"&amp;TEXT(MONTH($E$6),"00")&amp;"/"&amp;YEAR($E$6)&amp;"."</f>
-        <v>Forma de pagamento: Pix. Esta proposta é válida até 02/10/2026.</v>
+        <v>Forma de pagamento: Pix. Esta proposta é válida até 03/10/2026.</v>
       </c>
       <c r="B50" s="28" t="n"/>
       <c r="C50" s="28" t="n"/>

--- a/projetos/gestao-ia-planilhas/produto/kit-advogados/07-proposta-de-honorarios.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-advogados/07-proposta-de-honorarios.xlsx
@@ -352,7 +352,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="5">
     <dxf>
       <font>
         <name val="Arial"/>
@@ -363,6 +363,19 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="00FBE4E4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <b val="1"/>
+        <color rgb="00155E3C"/>
+        <sz val="10"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00DDF3E7"/>
         </patternFill>
       </fill>
     </dxf>
@@ -908,7 +921,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores e gráficos funcionam.</t>
+          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores, semáforos e gráficos funcionam: as regras de cor que dependem do mês escolhido em Config usam INDIRECT, que é a forma que o Sheets aceita para regra condicional apontar para outra aba.</t>
         </is>
       </c>
     </row>
@@ -932,7 +945,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os seus dados, troque a data de referência em Config por =HOJE(): daí em diante ela acompanha o dia.</t>
+          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os SEUS dados, troque em Config: a data de referência por =HOJE(), o ano, o mês do painel, o trimestre (onde houver) e a lista de feriados. Trocar só a data de referência deixa o resto apontando para 2026.</t>
         </is>
       </c>
     </row>
@@ -960,7 +973,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E58"/>
+  <dimension ref="A1:F58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1580,6 +1593,20 @@
         <v>4500</v>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" s="20" t="inlineStr">
+        <is>
+          <t>Confere com o valor da proposta?</t>
+        </is>
+      </c>
+      <c r="C45" s="20" t="str">
+        <f>IF(ABS(C44-$E$20)&lt;0.01,"Sim","NÃO: faltam "&amp;FIXED($E$20-C44,2)&amp;" sem vencimento. Ajuste a entrada ou o número de parcelas antes de enviar.")</f>
+        <v>Sim</v>
+      </c>
+      <c r="D45" s="28" t="n"/>
+      <c r="E45" s="28" t="n"/>
+      <c r="F45" s="29" t="n"/>
+    </row>
     <row r="46">
       <c r="A46" s="17" t="inlineStr">
         <is>
@@ -1668,8 +1695,9 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
-  <mergeCells count="9">
+  <mergeCells count="10">
     <mergeCell ref="A50:E50"/>
+    <mergeCell ref="C45:F45"/>
     <mergeCell ref="B8:E8"/>
     <mergeCell ref="A48:E48"/>
     <mergeCell ref="A2:E2"/>
@@ -1679,6 +1707,14 @@
     <mergeCell ref="B21:D21"/>
     <mergeCell ref="A3:E3"/>
   </mergeCells>
+  <conditionalFormatting sqref="C45">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>LEFT(C45,3)="NÃO"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="1">
+      <formula>C45="Sim"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="4">
     <dataValidation sqref="B7" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=OFFSET(Config!$D$14,0,0,MAX(1,COUNTA(Config!$D$14:$D$33)),1)</formula1>
@@ -1686,9 +1722,8 @@
     <dataValidation sqref="E7" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=OFFSET(Config!$F$14,0,0,MAX(1,COUNTA(Config!$F$14:$F$33)),1)</formula1>
     </dataValidation>
-    <dataValidation sqref="B25" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Parcelas do restante" error="Digite um número inteiro de 1 a 12. Use 0 apenas se a entrada quitar o valor todo." type="whole" operator="between">
-      <formula1>0</formula1>
-      <formula2>12</formula2>
+    <dataValidation sqref="B25" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Parcelas do restante" error="Digite um número inteiro de 1 a 12. Zero só é aceito quando a entrada quita o valor todo; com saldo em aberto, a proposta precisa de cronograma." type="custom">
+      <formula1>=AND(B25=INT(B25),B25&gt;=0,B25&lt;=12,OR(B25&gt;0,ROUND($E$20-E24,2)&lt;=0))</formula1>
     </dataValidation>
     <dataValidation sqref="E27" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=OFFSET(Config!$H$14,0,0,MAX(1,COUNTA(Config!$H$14:$H$33)),1)</formula1>
@@ -4686,15 +4721,15 @@
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>LEFT($L9,8)="Validade"</formula>
     </cfRule>
-    <cfRule type="expression" priority="2" dxfId="1">
+    <cfRule type="expression" priority="2" dxfId="2">
       <formula>LEFT($L9,5)="Vence"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J9:J108">
-    <cfRule type="expression" priority="3" dxfId="2">
+    <cfRule type="expression" priority="3" dxfId="3">
       <formula>$J9="Fechada"</formula>
     </cfRule>
-    <cfRule type="expression" priority="4" dxfId="3">
+    <cfRule type="expression" priority="4" dxfId="4">
       <formula>$J9="Perdida"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/projetos/gestao-ia-planilhas/produto/kit-advogados/07-proposta-de-honorarios.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-advogados/07-proposta-de-honorarios.xlsx
@@ -986,7 +986,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="5" t="str">
         <f>Config!$B$4&amp;" · Proposta de honorários · "&amp;TEXT(DAY($E$4),"00")&amp;"/"&amp;TEXT(MONTH($E$4),"00")&amp;"/"&amp;YEAR($E$4)</f>
-        <v>Ferraz &amp; Lima Advocacia (exemplo fictício) · Proposta de honorários · 18/09/2026</v>
+        <v>Ferraz &amp; Lima Advocacia (exemplo fictício) · Proposta de honorários · 19/09/2026</v>
       </c>
     </row>
     <row r="2">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="E4" s="10">
         <f>TODAY()</f>
-        <v>46283.0</v>
+        <v>46284.0</v>
       </c>
     </row>
     <row r="5">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="E6" s="12">
         <f>E4+E5</f>
-        <v>46298.0</v>
+        <v>46299.0</v>
       </c>
     </row>
     <row r="7">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="B32" s="12">
         <f>IF(1&gt;$B$25,"",$E$4+$B$26+(1-1)*$B$27)</f>
-        <v>46313.0</v>
+        <v>46314.0</v>
       </c>
       <c r="C32" s="24">
         <f>IF(1&gt;$B$25,"",$E$26)</f>
@@ -1435,7 +1435,7 @@
       </c>
       <c r="B33" s="12">
         <f>IF(2&gt;$B$25,"",$E$4+$B$26+(2-1)*$B$27)</f>
-        <v>46343.0</v>
+        <v>46344.0</v>
       </c>
       <c r="C33" s="24">
         <f>IF(2&gt;$B$25,"",$E$26)</f>
@@ -1449,7 +1449,7 @@
       </c>
       <c r="B34" s="12">
         <f>IF(3&gt;$B$25,"",$E$4+$B$26+(3-1)*$B$27)</f>
-        <v>46373.0</v>
+        <v>46374.0</v>
       </c>
       <c r="C34" s="24">
         <f>IF(3&gt;$B$25,"",$E$26)</f>
@@ -1650,7 +1650,7 @@
     <row r="50">
       <c r="A50" s="26" t="str">
         <f>"Forma de pagamento: "&amp;$E$27&amp;". Esta proposta é válida até "&amp;TEXT(DAY($E$6),"00")&amp;"/"&amp;TEXT(MONTH($E$6),"00")&amp;"/"&amp;YEAR($E$6)&amp;"."</f>
-        <v>Forma de pagamento: Pix. Esta proposta é válida até 03/10/2026.</v>
+        <v>Forma de pagamento: Pix. Esta proposta é válida até 04/10/2026.</v>
       </c>
       <c r="B50" s="28" t="n"/>
       <c r="C50" s="28" t="n"/>

--- a/projetos/gestao-ia-planilhas/produto/kit-advogados/07-proposta-de-honorarios.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-advogados/07-proposta-de-honorarios.xlsx
@@ -1309,7 +1309,7 @@
         </is>
       </c>
       <c r="E24" s="24">
-        <f>$E$20*B24</f>
+        <f>ROUND($E$20*B24,2)</f>
         <v>1800</v>
       </c>
     </row>
@@ -1343,11 +1343,11 @@
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>Valor de cada parcela (R$)</t>
+          <t>Valor da parcela (R$; a última fecha o centavo)</t>
         </is>
       </c>
       <c r="E26" s="24">
-        <f>IF(B25=0,0,E25/B25)</f>
+        <f>IF(B25=0,0,ROUND(E25/B25,2))</f>
         <v>900</v>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
         <v>46314.0</v>
       </c>
       <c r="C32" s="24">
-        <f>IF(1&gt;$B$25,"",$E$26)</f>
+        <f>IF(1&gt;$B$25,"",IF(1=$B$25,$E$25-$E$26*($B$25-1),$E$26))</f>
         <v>900</v>
       </c>
     </row>
@@ -1438,7 +1438,7 @@
         <v>46344.0</v>
       </c>
       <c r="C33" s="24">
-        <f>IF(2&gt;$B$25,"",$E$26)</f>
+        <f>IF(2&gt;$B$25,"",IF(2=$B$25,$E$25-$E$26*($B$25-1),$E$26))</f>
         <v>900</v>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
         <v>46374.0</v>
       </c>
       <c r="C34" s="24">
-        <f>IF(3&gt;$B$25,"",$E$26)</f>
+        <f>IF(3&gt;$B$25,"",IF(3=$B$25,$E$25-$E$26*($B$25-1),$E$26))</f>
         <v>900</v>
       </c>
     </row>
@@ -1466,7 +1466,7 @@
         <v/>
       </c>
       <c r="C35" s="24">
-        <f>IF(4&gt;$B$25,"",$E$26)</f>
+        <f>IF(4&gt;$B$25,"",IF(4=$B$25,$E$25-$E$26*($B$25-1),$E$26))</f>
         <v/>
       </c>
     </row>
@@ -1480,7 +1480,7 @@
         <v/>
       </c>
       <c r="C36" s="24">
-        <f>IF(5&gt;$B$25,"",$E$26)</f>
+        <f>IF(5&gt;$B$25,"",IF(5=$B$25,$E$25-$E$26*($B$25-1),$E$26))</f>
         <v/>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
         <v/>
       </c>
       <c r="C37" s="24">
-        <f>IF(6&gt;$B$25,"",$E$26)</f>
+        <f>IF(6&gt;$B$25,"",IF(6=$B$25,$E$25-$E$26*($B$25-1),$E$26))</f>
         <v/>
       </c>
     </row>
@@ -1508,7 +1508,7 @@
         <v/>
       </c>
       <c r="C38" s="24">
-        <f>IF(7&gt;$B$25,"",$E$26)</f>
+        <f>IF(7&gt;$B$25,"",IF(7=$B$25,$E$25-$E$26*($B$25-1),$E$26))</f>
         <v/>
       </c>
     </row>
@@ -1522,7 +1522,7 @@
         <v/>
       </c>
       <c r="C39" s="24">
-        <f>IF(8&gt;$B$25,"",$E$26)</f>
+        <f>IF(8&gt;$B$25,"",IF(8=$B$25,$E$25-$E$26*($B$25-1),$E$26))</f>
         <v/>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
         <v/>
       </c>
       <c r="C40" s="24">
-        <f>IF(9&gt;$B$25,"",$E$26)</f>
+        <f>IF(9&gt;$B$25,"",IF(9=$B$25,$E$25-$E$26*($B$25-1),$E$26))</f>
         <v/>
       </c>
     </row>
@@ -1550,7 +1550,7 @@
         <v/>
       </c>
       <c r="C41" s="24">
-        <f>IF(10&gt;$B$25,"",$E$26)</f>
+        <f>IF(10&gt;$B$25,"",IF(10=$B$25,$E$25-$E$26*($B$25-1),$E$26))</f>
         <v/>
       </c>
     </row>
@@ -1564,7 +1564,7 @@
         <v/>
       </c>
       <c r="C42" s="24">
-        <f>IF(11&gt;$B$25,"",$E$26)</f>
+        <f>IF(11&gt;$B$25,"",IF(11=$B$25,$E$25-$E$26*($B$25-1),$E$26))</f>
         <v/>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
         <v/>
       </c>
       <c r="C43" s="24">
-        <f>IF(12&gt;$B$25,"",$E$26)</f>
+        <f>IF(12&gt;$B$25,"",IF(12=$B$25,$E$25-$E$26*($B$25-1),$E$26))</f>
         <v/>
       </c>
     </row>

--- a/projetos/gestao-ia-planilhas/produto/kit-advogados/07-proposta-de-honorarios.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-advogados/07-proposta-de-honorarios.xlsx
@@ -793,6 +793,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="46" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -921,7 +922,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores, semáforos e gráficos funcionam: as regras de cor que dependem do mês escolhido em Config usam INDIRECT, que é a forma que o Sheets aceita para regra condicional apontar para outra aba.</t>
+          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores e semáforos funcionam: as regras de cor que dependem do mês escolhido em Config usam INDIRECT, que é a forma que o Sheets aceita para regra condicional apontar para outra aba.</t>
         </is>
       </c>
     </row>
@@ -986,7 +987,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="5" t="str">
         <f>Config!$B$4&amp;" · Proposta de honorários · "&amp;TEXT(DAY($E$4),"00")&amp;"/"&amp;TEXT(MONTH($E$4),"00")&amp;"/"&amp;YEAR($E$4)</f>
-        <v>Ferraz &amp; Lima Advocacia (exemplo fictício) · Proposta de honorários · 19/09/2026</v>
+        <v>Ferraz &amp; Lima Advocacia (exemplo fictício) · Proposta de honorários · 24/09/2026</v>
       </c>
     </row>
     <row r="2">
@@ -1020,7 +1021,7 @@
       </c>
       <c r="E4" s="10">
         <f>TODAY()</f>
-        <v>46284.0</v>
+        <v>46289.0</v>
       </c>
     </row>
     <row r="5">
@@ -1061,7 +1062,7 @@
       </c>
       <c r="E6" s="12">
         <f>E4+E5</f>
-        <v>46299.0</v>
+        <v>46304.0</v>
       </c>
     </row>
     <row r="7">
@@ -1421,7 +1422,7 @@
       </c>
       <c r="B32" s="12">
         <f>IF(1&gt;$B$25,"",$E$4+$B$26+(1-1)*$B$27)</f>
-        <v>46314.0</v>
+        <v>46319.0</v>
       </c>
       <c r="C32" s="24">
         <f>IF(1&gt;$B$25,"",IF(1=$B$25,$E$25-$E$26*($B$25-1),$E$26))</f>
@@ -1435,7 +1436,7 @@
       </c>
       <c r="B33" s="12">
         <f>IF(2&gt;$B$25,"",$E$4+$B$26+(2-1)*$B$27)</f>
-        <v>46344.0</v>
+        <v>46349.0</v>
       </c>
       <c r="C33" s="24">
         <f>IF(2&gt;$B$25,"",IF(2=$B$25,$E$25-$E$26*($B$25-1),$E$26))</f>
@@ -1449,7 +1450,7 @@
       </c>
       <c r="B34" s="12">
         <f>IF(3&gt;$B$25,"",$E$4+$B$26+(3-1)*$B$27)</f>
-        <v>46374.0</v>
+        <v>46379.0</v>
       </c>
       <c r="C34" s="24">
         <f>IF(3&gt;$B$25,"",IF(3=$B$25,$E$25-$E$26*($B$25-1),$E$26))</f>
@@ -1650,7 +1651,7 @@
     <row r="50">
       <c r="A50" s="26" t="str">
         <f>"Forma de pagamento: "&amp;$E$27&amp;". Esta proposta é válida até "&amp;TEXT(DAY($E$6),"00")&amp;"/"&amp;TEXT(MONTH($E$6),"00")&amp;"/"&amp;YEAR($E$6)&amp;"."</f>
-        <v>Forma de pagamento: Pix. Esta proposta é válida até 04/10/2026.</v>
+        <v>Forma de pagamento: Pix. Esta proposta é válida até 09/10/2026.</v>
       </c>
       <c r="B50" s="28" t="n"/>
       <c r="C50" s="28" t="n"/>
